--- a/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,90 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>319_尤加利叶带果_Eucalyptus leaves with small pods_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>432_小刺秦/情人果_small Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">460_袋鼠爪黄_Kangaroo Paw
+red /green /orange / yellow_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>422_粉黛_pink muhly grass_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>559_粉廖_Polygonum_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010107121083301410</v>
+        <v>01010712108330141081210510101010200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>559_粉廖_Polygonum_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010712108330141081210510101010200</v>
+        <v>010107121083301410812105101010102010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,92 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>707_永生吊米白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>5</v>
+      </c>
+      <c r="C26" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>845_干花紫罗兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>6</v>
+      </c>
+      <c r="C28" t="str">
+        <v>779_景天绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>755_豌豆花粉_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010107121083301410812105101010102010</v>
+        <v>010107121083301410812105101010102010510152515301015150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
@@ -693,6 +693,9 @@
       <c r="C31" t="str">
         <v>755_豌豆花粉_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -751,7 +754,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010107121083301410812105101010102010510152515301015150</v>
+        <v>0101071210833014108121051010101020105101525153010151510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-4.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -697,9 +697,17 @@
         <v>10</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>333_狼尾草_wolf tail grass_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -754,7 +762,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101071210833014108121051010101020105101525153010151510</v>
+        <v>010107121083301410812105101010102010510152515301015151015</v>
       </c>
     </row>
   </sheetData>
